--- a/xls/square_16_quad4_17.xlsx
+++ b/xls/square_16_quad4_17.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>324</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>289</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>675</v>
+      </c>
+      <c r="I15">
+        <v>1.4893492856928083</v>
+      </c>
+      <c r="J15">
+        <v>-0.4677037919308493</v>
+      </c>
+      <c r="K15">
+        <v>0.3603884356197957</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>324</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>289</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>768</v>
+      </c>
+      <c r="I16">
+        <v>0.6991206148528467</v>
+      </c>
+      <c r="J16">
+        <v>-0.7622003232831475</v>
+      </c>
+      <c r="K16">
+        <v>-0.012294029668322246</v>
+      </c>
+    </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>11</v>
@@ -482,13 +552,13 @@
         <v>867</v>
       </c>
       <c r="I17">
-        <v>-0.17307484160093414</v>
+        <v>-1.1038483055606068</v>
       </c>
       <c r="J17">
-        <v>-1.8433615300794348</v>
+        <v>-1.5226049526106105</v>
       </c>
       <c r="K17">
-        <v>0.5150749227703371</v>
+        <v>0.28517992776859796</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -517,13 +587,13 @@
         <v>972</v>
       </c>
       <c r="I18">
-        <v>-1.8882963346977293</v>
+        <v>-1.5454455798066493</v>
       </c>
       <c r="J18">
-        <v>-1.8875831221636208</v>
+        <v>-1.5910088613169786</v>
       </c>
       <c r="K18">
-        <v>0.5444170306320486</v>
+        <v>0.5415054774840748</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -552,13 +622,13 @@
         <v>1083</v>
       </c>
       <c r="I19">
-        <v>-1.8816104475305613</v>
+        <v>-1.472116116221057</v>
       </c>
       <c r="J19">
-        <v>-1.880455393767261</v>
+        <v>-1.5576220520019897</v>
       </c>
       <c r="K19">
-        <v>0.8607747390580514</v>
+        <v>1.9264324431773803</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -587,13 +657,13 @@
         <v>1200</v>
       </c>
       <c r="I20">
-        <v>-1.8746129827897005</v>
+        <v>-1.4261644415702734</v>
       </c>
       <c r="J20">
-        <v>-1.8659849387536493</v>
+        <v>-1.523524879234569</v>
       </c>
       <c r="K20">
-        <v>1.5515863286538396</v>
+        <v>3.444666888775756</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -622,13 +692,13 @@
         <v>1323</v>
       </c>
       <c r="I21">
-        <v>-1.8449737551947483</v>
+        <v>-1.805206014241794</v>
       </c>
       <c r="J21">
-        <v>-1.790279409495216</v>
+        <v>-1.5573817945289166</v>
       </c>
       <c r="K21">
-        <v>2.320468915035521</v>
+        <v>4.242199255742352</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -657,13 +727,13 @@
         <v>1452</v>
       </c>
       <c r="I22">
-        <v>-1.638740274313676</v>
+        <v>-0.2716128677179078</v>
       </c>
       <c r="J22">
-        <v>-1.2159199605183064</v>
+        <v>-0.2746669810860714</v>
       </c>
       <c r="K22">
-        <v>3.3225983145251603</v>
+        <v>4.885123742978418</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -692,13 +762,13 @@
         <v>1587</v>
       </c>
       <c r="I23">
-        <v>-0.46952915347806407</v>
+        <v>-0.0011205346924207274</v>
       </c>
       <c r="J23">
-        <v>-0.3219275667190296</v>
+        <v>-0.0009226049315509989</v>
       </c>
       <c r="K23">
-        <v>3.7982585248589866</v>
+        <v>3.859548873613345</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -727,13 +797,13 @@
         <v>1728</v>
       </c>
       <c r="I24">
-        <v>-0.029236788847919918</v>
+        <v>-0.0003877353581491114</v>
       </c>
       <c r="J24">
-        <v>-0.024163313492294766</v>
+        <v>-0.0003373934464399477</v>
       </c>
       <c r="K24">
-        <v>3.530381261427767</v>
+        <v>3.661126369775932</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -762,13 +832,13 @@
         <v>1875</v>
       </c>
       <c r="I25">
-        <v>-0.007605231948023234</v>
+        <v>-0.00011665329975581531</v>
       </c>
       <c r="J25">
-        <v>-0.006076882814754217</v>
+        <v>-9.858234226681428e-5</v>
       </c>
       <c r="K25">
-        <v>3.283172366800984</v>
+        <v>3.399261640463251</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -797,13 +867,13 @@
         <v>2028</v>
       </c>
       <c r="I26">
-        <v>-0.0008712894101549463</v>
+        <v>-1.3912370862816558e-5</v>
       </c>
       <c r="J26">
-        <v>-0.0006999586753632965</v>
+        <v>-1.1859172686293172e-5</v>
       </c>
       <c r="K26">
-        <v>2.8553910247163388</v>
+        <v>2.9535837642598675</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -832,13 +902,13 @@
         <v>2187</v>
       </c>
       <c r="I27">
-        <v>-0.0005051129149431721</v>
+        <v>-8.39798917953266e-6</v>
       </c>
       <c r="J27">
-        <v>-0.0004199297598080732</v>
+        <v>-7.1424362277853976e-6</v>
       </c>
       <c r="K27">
-        <v>2.7553949802985147</v>
+        <v>2.852464813182453</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -867,13 +937,13 @@
         <v>2352</v>
       </c>
       <c r="I28">
-        <v>-0.00020909627247894333</v>
+        <v>-3.0579668759149167e-6</v>
       </c>
       <c r="J28">
-        <v>-0.0001905417261328171</v>
+        <v>-2.821229808744066e-6</v>
       </c>
       <c r="K28">
-        <v>2.6011349803231836</v>
+        <v>2.6618403513132356</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -902,13 +972,13 @@
         <v>2523</v>
       </c>
       <c r="I29">
-        <v>-9.500637155054834e-5</v>
+        <v>-9.741802539694696e-7</v>
       </c>
       <c r="J29">
-        <v>-8.817621681892506e-5</v>
+        <v>-8.985726688939654e-7</v>
       </c>
       <c r="K29">
-        <v>2.441362975548944</v>
+        <v>2.4145745440131194</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -937,13 +1007,13 @@
         <v>2700</v>
       </c>
       <c r="I30">
-        <v>-0.00015905337279765235</v>
+        <v>-1.4629593803953863e-6</v>
       </c>
       <c r="J30">
-        <v>-0.00013702434015431587</v>
+        <v>-1.2596894473592706e-6</v>
       </c>
       <c r="K30">
-        <v>2.5196075124950426</v>
+        <v>2.466200235520889</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -972,13 +1042,13 @@
         <v>2883</v>
       </c>
       <c r="I31">
-        <v>-0.0002633221688999199</v>
+        <v>-2.5849545247950857e-6</v>
       </c>
       <c r="J31">
-        <v>-0.0002384182443301557</v>
+        <v>-2.339674383505022e-6</v>
       </c>
       <c r="K31">
-        <v>2.6391937926322004</v>
+        <v>2.60019362357667</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1007,13 +1077,13 @@
         <v>3072</v>
       </c>
       <c r="I32">
-        <v>-0.0002467671723564087</v>
+        <v>-2.0820344001081415e-6</v>
       </c>
       <c r="J32">
-        <v>-0.00024979249309309585</v>
+        <v>-2.1111636900590378e-6</v>
       </c>
       <c r="K32">
-        <v>2.659028929953206</v>
+        <v>2.5874230197850157</v>
       </c>
     </row>
   </sheetData>
